--- a/SGC-CKN/Excel/8abde189-cc63-42a2-aaae-fc2fa32b637a_Lô_CT-02_PT-71_D800_25-03-2026.xlsx
+++ b/SGC-CKN/Excel/8abde189-cc63-42a2-aaae-fc2fa32b637a_Lô_CT-02_PT-71_D800_25-03-2026.xlsx
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>PT-71</t>
+    <t>P7-71</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>
@@ -59,7 +59,7 @@
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>08:25 25/03/2026</t>
+    <t>08:23 25/03/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -171,7 +171,7 @@
     <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">02:56
+    <t xml:space="preserve">02:36
 25/03/2026</t>
   </si>
   <si>
@@ -1249,7 +1249,7 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-3.65</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <v>-6.96</v>
@@ -1258,10 +1258,10 @@
         <v>0.37</v>
       </c>
       <c r="I11" s="5">
-        <v>3.31</v>
+        <v>6.96</v>
       </c>
       <c r="J11" s="8">
-        <v>9.03</v>
+        <v>18.98</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1430,13 +1430,13 @@
         <v>-35.85</v>
       </c>
       <c r="H16" s="21">
-        <v>1.43</v>
+        <v>1.77</v>
       </c>
       <c r="I16" s="21">
         <v>10.2</v>
       </c>
       <c r="J16" s="8">
-        <v>7.12</v>
+        <v>5.77</v>
       </c>
       <c r="K16" s="22" t="s">
         <v>30</v>
@@ -1462,16 +1462,16 @@
         <v>-35.85</v>
       </c>
       <c r="G17" s="24">
-        <v>-38.52</v>
+        <v>-38.32</v>
       </c>
       <c r="H17" s="24">
         <v>0.63</v>
       </c>
       <c r="I17" s="24">
-        <v>2.67</v>
+        <v>2.47</v>
       </c>
       <c r="J17" s="27">
-        <v>4.22</v>
+        <v>3.9</v>
       </c>
       <c r="K17" s="25" t="s">
         <v>30</v>
@@ -1494,7 +1494,7 @@
         <v>58</v>
       </c>
       <c r="F18" s="28">
-        <v>-38.52</v>
+        <v>-38.32</v>
       </c>
       <c r="G18" s="28">
         <v>-39.8</v>
@@ -1503,10 +1503,10 @@
         <v>0.63</v>
       </c>
       <c r="I18" s="28">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="J18" s="27">
-        <v>2.02</v>
+        <v>2.34</v>
       </c>
       <c r="K18" s="29" t="s">
         <v>30</v>
@@ -1731,7 +1731,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-3.65</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>-6.96</v>
@@ -1740,10 +1740,10 @@
         <v>0.37</v>
       </c>
       <c r="H2" s="5">
-        <v>3.31</v>
+        <v>6.96</v>
       </c>
       <c r="I2" s="8">
-        <v>9.03</v>
+        <v>18.98</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1882,13 +1882,13 @@
         <v>-35.85</v>
       </c>
       <c r="G7" s="21">
-        <v>1.43</v>
+        <v>1.77</v>
       </c>
       <c r="H7" s="21">
         <v>10.2</v>
       </c>
       <c r="I7" s="8">
-        <v>7.12</v>
+        <v>5.77</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1908,16 +1908,16 @@
         <v>-35.85</v>
       </c>
       <c r="F8" s="24">
-        <v>-38.52</v>
+        <v>-38.32</v>
       </c>
       <c r="G8" s="24">
         <v>0.63</v>
       </c>
       <c r="H8" s="24">
-        <v>2.67</v>
+        <v>2.47</v>
       </c>
       <c r="I8" s="27">
-        <v>4.22</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1934,7 +1934,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="28">
-        <v>-38.52</v>
+        <v>-38.32</v>
       </c>
       <c r="F9" s="28">
         <v>-39.8</v>
@@ -1943,10 +1943,10 @@
         <v>0.63</v>
       </c>
       <c r="H9" s="28">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="I9" s="27">
-        <v>2.02</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2021,19 +2021,19 @@
         <v>10</v>
       </c>
       <c r="E12" s="40">
-        <v>-3.65</v>
+        <v>0</v>
       </c>
       <c r="F12" s="40">
         <v>-45.02</v>
       </c>
       <c r="G12" s="40">
-        <v>8.9</v>
+        <v>9.23</v>
       </c>
       <c r="H12" s="40">
-        <v>41.37</v>
+        <v>45.02</v>
       </c>
       <c r="I12" s="40">
-        <v>4.65</v>
+        <v>4.88</v>
       </c>
     </row>
   </sheetData>
